--- a/www/download/IND.surplus_value.empe.r.pc.WIOD13.xlsx
+++ b/www/download/IND.surplus_value.empe.r.pc.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.46</t>
+          <t>0.664844094008637</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>61.65</t>
+          <t>0.616696794197378</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>66.88</t>
+          <t>0.668985359282772</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.35</t>
+          <t>0.663544394756668</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>57.75</t>
+          <t>0.550489990046533</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>65.08</t>
+          <t>0.650897775902082</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.55</t>
+          <t>0.695848438386212</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>62.11</t>
+          <t>0.621419051918678</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>0.523926082941304</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>0.326023948583167</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>0.26107422558239</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>0.29397441571674</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>0.272732491000702</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>0.405050961176974</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>0.464646290511381</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.033357685786122</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>0.0720589940316576</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>0.263806554278025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>0.245727945113809</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>0.216239868288463</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>0.293132449639178</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>0.278105792142808</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0.270210499894918</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>0.170680878597897</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>0.124580450270297</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>0.109617849487596</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0952465910759184</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>0.102612346552772</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>0.14875983656028</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>0.228994226578118</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-20.64</t>
+          <t>-0.20636267720071</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-0.223008015401268</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-18.6</t>
+          <t>-0.185922462834386</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-18.11</t>
+          <t>-0.181125944951323</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-25.14</t>
+          <t>-0.263511802764856</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-26.64</t>
+          <t>-0.266307796383915</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>-0.307269571139718</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-36.1</t>
+          <t>-0.360897406278184</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-47.64</t>
+          <t>-0.476351696266912</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.1</t>
+          <t>-0.501045783205563</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-49.11</t>
+          <t>-0.491081617221662</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-48.27</t>
+          <t>-0.482722623409206</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-45.31</t>
+          <t>-0.453057102095001</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-39.2</t>
+          <t>-0.391948440666127</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-42.46</t>
+          <t>-0.42458814850012</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>261.67</t>
+          <t>2.6169025688239</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>305.57</t>
+          <t>3.05584448543903</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>359.87</t>
+          <t>3.59886622848295</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>268.19</t>
+          <t>2.6818930045425</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>305.92</t>
+          <t>2.97536687155778</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>323.6</t>
+          <t>3.23611625908966</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>313.75</t>
+          <t>3.1377471743588</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>332.06</t>
+          <t>3.32106933520339</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>330.72</t>
+          <t>3.30741394113146</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>341.48</t>
+          <t>3.4147345864548</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>355.64</t>
+          <t>3.55649795293658</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>372.9</t>
+          <t>3.7294247514949</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>358.63</t>
+          <t>3.58663989939486</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>332.31</t>
+          <t>3.32281361917781</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>288.39</t>
+          <t>2.88394621823645</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>201.42</t>
+          <t>2.0144710854141</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>206.43</t>
+          <t>2.0645462442694</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>224.09</t>
+          <t>2.24112458875961</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>221.54</t>
+          <t>2.21535951516919</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>254.48</t>
+          <t>2.46914373891971</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>267.11</t>
+          <t>2.6713164734239</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>282.75</t>
+          <t>2.82791359992214</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>297.8</t>
+          <t>2.97844425766529</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>306.38</t>
+          <t>3.06389484340434</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>301.87</t>
+          <t>3.01858745535524</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>282.22</t>
+          <t>2.82231123931332</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>278.67</t>
+          <t>2.78702010382325</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>276.13</t>
+          <t>2.76175758959148</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>263.44</t>
+          <t>2.63450173131125</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>262.23</t>
+          <t>2.62249139844803</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>81.86</t>
+          <t>0.819067980762562</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>0.898416863288134</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>101.79</t>
+          <t>1.01818932020322</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>0.895169722566085</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>81.37</t>
+          <t>0.777608600796331</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>0.672150260261082</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>0.578140284648387</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>58.06</t>
+          <t>0.581054276667937</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>48.26</t>
+          <t>0.482751281082752</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>43.36</t>
+          <t>0.433637497963682</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>0.331313512715291</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>0.286275045246928</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>0.347996371157151</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>0.376245743296671</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>0.491564587129318</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-30.96</t>
+          <t>-0.309556659338431</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-27.66</t>
+          <t>-0.276570415131229</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-25.39</t>
+          <t>-0.253882672223445</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-0.220059277956098</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>-0.192440531132746</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-0.114982066780616</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-0.0325508240325502</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>0.0328806771209706</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.105271561580323</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>0.16915221058041</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>0.234501924664957</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>0.280848654676076</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>0.426525146747572</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>44.66</t>
+          <t>0.446546116228874</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>0.491925223886913</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>0.873857773524042</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>81.95</t>
+          <t>0.819660071006088</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>110.3</t>
+          <t>1.10312329070225</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>102.88</t>
+          <t>1.02882384867275</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>0.823858758799705</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>0.90968125376066</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>0.756234586148946</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>72.01</t>
+          <t>0.720346919004516</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>52.66</t>
+          <t>0.526774092699628</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>58.36</t>
+          <t>0.583577663736276</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>62.27</t>
+          <t>0.622732944797972</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>0.652279328797231</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>0.833577944555002</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>0.579591180873721</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>93.65</t>
+          <t>0.93661589540497</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>358.31</t>
+          <t>3.58455805443664</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>221.22</t>
+          <t>2.21223675858389</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>246.06</t>
+          <t>2.46071247713598</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>240.62</t>
+          <t>2.40608686539258</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>242.73</t>
+          <t>2.3930771937607</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>256.66</t>
+          <t>2.56668166143455</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>223.97</t>
+          <t>2.23984217463219</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>210.59</t>
+          <t>2.10629164968625</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>182.03</t>
+          <t>1.82052562182535</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>163.33</t>
+          <t>1.63321676798694</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>154.84</t>
+          <t>1.54842517502599</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>164.7</t>
+          <t>1.64707582191896</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>160.28</t>
+          <t>1.6030912000641</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>166.06</t>
+          <t>1.66067335116443</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>204.68</t>
+          <t>2.04688528031083</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-10.1</t>
+          <t>-0.100868858370613</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.0112657389033515</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>0.124291357436849</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0907126976615102</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>0.0484953857286503</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>0.0160428476212013</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.0385457566174241</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>0.0364557817068178</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-0.0988619489501354</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-0.110369395595864</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-0.0727805351891223</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-0.0730943530456774</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-8.66</t>
+          <t>-0.0860447043019229</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.0298834021187613</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.00665368648313613</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-0.143835648494065</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-12.28</t>
+          <t>-0.122761536619317</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>0.149884927087773</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0539506512729584</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>0.0309812943052392</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>0.0996803919451164</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>0.0569544391835801</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.017307352657834</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-0.115668307016842</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-11.99</t>
+          <t>-0.119872014305954</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-0.116791941691676</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-0.118930354850695</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-0.110803636470346</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-0.0473235291871613</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>0.060891348553175</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>55.61</t>
+          <t>0.556358921948127</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>0.629851986848134</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>93.23</t>
+          <t>0.932394537573213</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>77.81</t>
+          <t>0.777976501337163</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>0.657457268316791</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>0.714239741107747</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>61.81</t>
+          <t>0.618292793773097</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>0.54610350813783</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>0.401906667555281</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>0.349269588923848</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>33.07</t>
+          <t>0.330774241801549</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>0.308815236552019</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0.320088061048499</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>35.23</t>
+          <t>0.352319275672162</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>50.08</t>
+          <t>0.500842814779388</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>301.2</t>
+          <t>3.01256768261564</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>271.38</t>
+          <t>2.71435059374569</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>257.73</t>
+          <t>2.5775262344942</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>234.92</t>
+          <t>2.34932746255004</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>242.91</t>
+          <t>2.37619102811299</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>195.15</t>
+          <t>1.9520130564143</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>191.43</t>
+          <t>1.9152175004044</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>134.72</t>
+          <t>1.34756215676968</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>1.00569894917218</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>94.55</t>
+          <t>0.946372632337393</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>111.47</t>
+          <t>1.11481010433858</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>118.29</t>
+          <t>1.1833772861168</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>110.04</t>
+          <t>1.10060632939046</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>92.84</t>
+          <t>0.928531171789567</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>99.29</t>
+          <t>0.993058048985329</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>31.59</t>
+          <t>0.317445273926105</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>28.98</t>
+          <t>0.291646153348776</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.546247946914294</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>0.454862797572739</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>0.426012976330255</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>0.596968599587378</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>54.79</t>
+          <t>0.549115729642496</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>52.93</t>
+          <t>0.530054847412534</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>0.371776383734726</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.310313585115714</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>0.283722746993507</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>0.240128851301592</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>0.245855010649923</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>0.277679764933525</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>0.351682620883037</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>0.219749526915392</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22.48</t>
+          <t>0.224857364886879</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>0.420256068514902</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>0.283521195927008</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>0.183061983423418</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>0.19503106751445</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>0.132774948580576</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>0.0779549785864448</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.0111547856108607</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-0.0295739265229609</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-0.0344959911068048</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.0128566941662587</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.00771322514455752</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0476657466575143</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>0.129853684196019</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>55.48</t>
+          <t>0.554839193089609</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>0.539034726825145</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>0.65434093417811</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>0.520182455271668</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>0.413312132586082</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>0.376327641774193</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>0.311803822996247</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>0.269006973571893</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>0.183881647520094</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>0.119030284308386</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>0.123536959428809</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>0.118006171945475</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>0.149570274549424</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>29.64</t>
+          <t>0.296451767226101</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>0.406999241892006</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>147.03</t>
+          <t>1.47034695670764</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>135.82</t>
+          <t>1.35821822685476</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>142.27</t>
+          <t>1.42272641068373</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>147.48</t>
+          <t>1.47480360924895</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>132.99</t>
+          <t>1.31038598273104</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>1.21302391588735</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>133.09</t>
+          <t>1.33114398597743</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>104.15</t>
+          <t>1.04179781857684</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>100.21</t>
+          <t>1.00221066758032</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>100.23</t>
+          <t>1.00242427271009</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>105.86</t>
+          <t>1.05835397741749</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>103.6</t>
+          <t>1.03606829872304</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>93.01</t>
+          <t>0.930280988255957</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>91.05</t>
+          <t>0.910778155302891</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>0.873469911429823</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>161.33</t>
+          <t>1.61379940078221</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>173.36</t>
+          <t>1.7339738724252</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>193.49</t>
+          <t>1.93526756570061</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>199.45</t>
+          <t>1.99450635375926</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>191.62</t>
+          <t>1.84266250509016</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>188.25</t>
+          <t>1.88283309798923</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>201.94</t>
+          <t>2.01991747388559</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>179.44</t>
+          <t>1.79512109931393</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>159.28</t>
+          <t>1.59312694421219</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>199.62</t>
+          <t>1.99601526876392</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>204.28</t>
+          <t>2.04301031692069</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>221.2</t>
+          <t>2.21247183268766</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>210.16</t>
+          <t>2.10213621223911</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>236.3</t>
+          <t>2.36317932228717</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>263.97</t>
+          <t>2.63978053294893</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>1.02107283852836</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>109.2</t>
+          <t>1.09199277252593</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>142.47</t>
+          <t>1.42472455306349</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>1.53442521229929</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>161.38</t>
+          <t>1.59992212229481</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>138.83</t>
+          <t>1.38828650312971</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>138.44</t>
+          <t>1.38447420091753</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>135.22</t>
+          <t>1.35229081131378</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>113.38</t>
+          <t>1.13377246463403</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>1.21120396275009</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>103.15</t>
+          <t>1.03153729163087</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>0.939246160313174</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>81.27</t>
+          <t>0.812732704463837</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>86.29</t>
+          <t>0.862878312955053</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>0.796041609335486</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>0.409134471702598</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>55.21</t>
+          <t>0.552140182969837</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>48.97</t>
+          <t>0.489721783380316</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>0.518515440790042</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>55.31</t>
+          <t>0.539903277550335</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>0.589589822843162</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>57.51</t>
+          <t>0.575128262938946</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>0.610588897356541</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>0.539784578242209</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>48.14</t>
+          <t>0.48140849844595</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>0.435932981838553</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>0.401907031150005</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>43.64</t>
+          <t>0.43646140362619</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>0.492395317536503</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>43.36</t>
+          <t>0.4335789980355</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>56.21</t>
+          <t>0.562609825007483</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>0.540105790048686</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>76.66</t>
+          <t>0.766830380641449</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>85.66</t>
+          <t>0.856670358253426</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>87.24</t>
+          <t>0.84501391030745</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>85.45</t>
+          <t>0.854793918955996</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>67.55</t>
+          <t>0.675812192162211</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>0.573844390239182</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>73.92</t>
+          <t>0.739390095256908</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>83.55</t>
+          <t>0.83554806769672</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>65.07</t>
+          <t>0.650825764633821</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>66.63</t>
+          <t>0.666353020468547</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>0.528683441016161</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>0.458239710083075</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>0.318958963639641</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>0.500768604718987</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>0.535957686939591</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>0.6693538651754</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>0.668789149947363</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>0.633510694330555</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>0.65981924650601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>58.32</t>
+          <t>0.583250452656939</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>53.69</t>
+          <t>0.537280772041591</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>39.34</t>
+          <t>0.393643059248438</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>0.309840043697237</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>0.304373046295864</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>0.291019926029989</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>35.55</t>
+          <t>0.355651640560817</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>0.44329083016187</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>0.588460140249154</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>0.244411974067843</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>0.414275116549566</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>56.95</t>
+          <t>0.569901278248372</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.98</t>
+          <t>0.619799970214295</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>0.499277017776594</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>0.435261165717034</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>0.453733203758505</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>51.53</t>
+          <t>0.516190221168899</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>0.47884812526799</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>0.39829366481715</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>38.61</t>
+          <t>0.38680637283641</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.460864099280051</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>61.58</t>
+          <t>0.616078794618852</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>66.01</t>
+          <t>0.660280516006552</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>0.59031763859863</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>64.27</t>
+          <t>0.642909617692244</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>67.21</t>
+          <t>0.672292562213195</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>0.833239632962865</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>102.68</t>
+          <t>1.0267284191536</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>108.99</t>
+          <t>1.05195368170717</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>100.32</t>
+          <t>1.00344825565788</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>99.45</t>
+          <t>0.995068290308986</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>0.961750654015098</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>83.69</t>
+          <t>0.837125074236327</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>84.05</t>
+          <t>0.840587397755457</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>0.794108647777444</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>73.93</t>
+          <t>0.739383039009935</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>77.57</t>
+          <t>0.775999338199113</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>93.95</t>
+          <t>0.939278877319591</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>1.04622313075151</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>238.67</t>
+          <t>2.38637378262752</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>218.93</t>
+          <t>2.18905724747554</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>222.33</t>
+          <t>2.22362357511729</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>173.92</t>
+          <t>1.73928686431718</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>160.38</t>
+          <t>1.57660085264172</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>162.58</t>
+          <t>1.62574654417079</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>163.37</t>
+          <t>1.63408904426126</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>155.2</t>
+          <t>1.55235521415243</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>131.28</t>
+          <t>1.31240328655462</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>169.55</t>
+          <t>1.69541085481745</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>165.14</t>
+          <t>1.65186275062019</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>157.75</t>
+          <t>1.57803654897146</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>169.17</t>
+          <t>1.69189909254302</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>153.97</t>
+          <t>1.53971331258022</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>160.63</t>
+          <t>1.60633374081393</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>0.0709825314758785</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.76</t>
+          <t>0.237638891126739</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>0.472395073779802</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>0.492627921398463</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>0.394773507175308</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>0.405219970051771</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>53.65</t>
+          <t>0.53649953687893</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>43.94</t>
+          <t>0.439770354146574</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>37.32</t>
+          <t>0.373541185641957</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>0.332927108698772</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>0.27943020075115</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>32.44</t>
+          <t>0.324503915011842</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>0.509889812332136</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>0.347365273088408</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>0.578505855214771</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>268.11</t>
+          <t>2.68166252795959</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>243.44</t>
+          <t>2.4348003817549</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>251.5</t>
+          <t>2.51526848862731</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>246.88</t>
+          <t>2.4688587108623</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>2.41247416626894</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>297.09</t>
+          <t>2.97131648773197</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>304.09</t>
+          <t>3.04155632321116</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>316.55</t>
+          <t>3.1660298615198</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>296.77</t>
+          <t>2.96803515331091</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>297.85</t>
+          <t>2.9785173285809</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>279.67</t>
+          <t>2.79690460652117</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>254.17</t>
+          <t>2.54219067765049</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>209.86</t>
+          <t>2.09897909851991</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>174.35</t>
+          <t>1.74319683842794</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>207.99</t>
+          <t>2.07988807771577</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>312.82</t>
+          <t>3.12845361438949</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>337.12</t>
+          <t>3.37143917541964</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>365.89</t>
+          <t>3.65917523333676</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>332.7</t>
+          <t>3.32695656930321</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>310.39</t>
+          <t>3.02046702669818</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>300.23</t>
+          <t>3.00245867709059</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>259.49</t>
+          <t>2.59567400078146</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>262.55</t>
+          <t>2.62633022126905</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>267.92</t>
+          <t>2.67947401334434</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>284.58</t>
+          <t>2.84588060496828</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>295.81</t>
+          <t>2.9583260329054</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>317.29</t>
+          <t>3.17322397197812</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>332.27</t>
+          <t>3.32324457799507</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>344.07</t>
+          <t>3.44058758627937</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>345.29</t>
+          <t>3.45302562794458</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>142.15</t>
+          <t>1.4218411677151</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>127.08</t>
+          <t>1.27107557932874</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>179.52</t>
+          <t>1.79542256084558</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>159.16</t>
+          <t>1.59151957512734</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>130.97</t>
+          <t>1.26817586258693</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>118.57</t>
+          <t>1.18594669489125</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>0.654156597127359</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>83.11</t>
+          <t>0.83141165583137</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>0.585589219975193</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>1.06893987378227</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>105.99</t>
+          <t>1.05989509655453</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>111.87</t>
+          <t>1.11883614359153</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>102.11</t>
+          <t>1.02139041377676</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>85.91</t>
+          <t>0.859109517351654</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>108.93</t>
+          <t>1.08933061662603</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-29</t>
+          <t>-0.290022091483555</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-25.22</t>
+          <t>-0.252255906926992</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>0.0884739322565187</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-0.102593932705593</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-14.99</t>
+          <t>-0.16197826592883</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-9.8</t>
+          <t>-0.0979724981618818</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-18.31</t>
+          <t>-0.183103032739698</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-26.95</t>
+          <t>-0.269415100996614</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-26.16</t>
+          <t>-0.261583521951536</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-25.35</t>
+          <t>-0.253531201866518</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-23.1</t>
+          <t>-0.231040356939442</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-23.2</t>
+          <t>-0.231960336215388</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-0.225853883363879</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-25.79</t>
+          <t>-0.257857952054785</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-23.02</t>
+          <t>-0.230219570609057</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>80.84</t>
+          <t>0.808531613717184</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>0.71689188349351</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>70.23</t>
+          <t>0.702396388928244</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.27</t>
+          <t>0.652700939205581</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>78.41</t>
+          <t>0.76942662345093</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>0.898733640922485</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>141.33</t>
+          <t>1.41344694776047</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>148.86</t>
+          <t>1.48887122586682</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>159.07</t>
+          <t>1.59087829922428</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>175.3</t>
+          <t>1.75292945623324</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>164.59</t>
+          <t>1.645988784626</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>172.98</t>
+          <t>1.7301064207366</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>175.72</t>
+          <t>1.75751160842962</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>163.84</t>
+          <t>1.63850937685121</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>190.22</t>
+          <t>1.90220181737619</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>96.41</t>
+          <t>0.96424460390865</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>0.929208279286328</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>124.47</t>
+          <t>1.24482283979873</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>105.53</t>
+          <t>1.05526969210018</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>109.02</t>
+          <t>1.06055785242647</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>105.4</t>
+          <t>1.05417026500341</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>97.45</t>
+          <t>0.974621377998517</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>100.27</t>
+          <t>1.00294549489716</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>0.94171426512374</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>96.19</t>
+          <t>0.961932443739747</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>0.989711254352635</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>119.47</t>
+          <t>1.19483031450807</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>120.51</t>
+          <t>1.20526980036987</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>113.41</t>
+          <t>1.13401219538881</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>150.67</t>
+          <t>1.5067497661447</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>144.26</t>
+          <t>1.44270094918391</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>150.7</t>
+          <t>1.50706528327688</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>179.74</t>
+          <t>1.79752670657526</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>123.14</t>
+          <t>1.2313586834088</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>122.47</t>
+          <t>1.21108416910677</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>0.909069136837895</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>78.42</t>
+          <t>0.784271877567775</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>137.96</t>
+          <t>1.37977927661821</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>131.72</t>
+          <t>1.3172674948632</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>180.19</t>
+          <t>1.80191570850497</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>144.68</t>
+          <t>1.44683604891193</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>158.83</t>
+          <t>1.58870869497918</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>145.02</t>
+          <t>1.450449965996</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>128.15</t>
+          <t>1.28122167342307</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>155.22</t>
+          <t>1.55224345940455</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>111.95</t>
+          <t>1.11958014063987</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>1.01510395493864</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>119.97</t>
+          <t>1.19973829776522</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>132.82</t>
+          <t>1.32812955661754</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>149.91</t>
+          <t>1.48334020184529</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>1.2390471285674</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>129.14</t>
+          <t>1.29158305290244</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>121.26</t>
+          <t>1.21269083988145</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>102.32</t>
+          <t>1.02323203313717</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>95.09</t>
+          <t>0.950890593971817</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>0.886729720430563</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>0.904277843342826</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>0.727652465270413</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>50.59</t>
+          <t>0.505818513139747</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>0.490635778672349</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>415.09</t>
+          <t>4.15153830763465</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>379.86</t>
+          <t>3.79898455623913</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>396.45</t>
+          <t>3.96498257198977</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>390.53</t>
+          <t>3.90527826450925</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>419.42</t>
+          <t>4.11378203287712</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>404.85</t>
+          <t>4.04876743206652</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>391.68</t>
+          <t>3.91765656659534</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>381.05</t>
+          <t>3.81125654881346</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>313.26</t>
+          <t>3.13252164645697</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>240.3</t>
+          <t>2.4029336068921</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>243.31</t>
+          <t>2.43344610376457</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>222.38</t>
+          <t>2.22392470194022</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>174.88</t>
+          <t>1.74820715985351</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>184.29</t>
+          <t>1.84272797275693</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>133.61</t>
+          <t>1.33611632206327</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>47.14</t>
+          <t>0.471842594160493</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>51.77</t>
+          <t>0.517902207223846</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>0.706924068982117</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.77</t>
+          <t>0.617748573686766</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>61.66</t>
+          <t>0.590370405021677</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>63.46</t>
+          <t>0.634703607984231</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>58.65</t>
+          <t>0.586354938656052</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>57.56</t>
+          <t>0.575740188447942</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>0.415019651458647</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>49.26</t>
+          <t>0.492324761279078</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>54.97</t>
+          <t>0.549568899333143</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>56.51</t>
+          <t>0.565071745112268</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>0.608834235846929</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>0.192387976884394</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>0.213405072396614</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>0.289558694147079</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0.260284595730465</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>0.453727324576592</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>0.354783139745114</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>0.327079089309456</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>0.248259529618917</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0.239285441307665</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>0.188987854888159</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>0.0972220627646851</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>0.0672048268603955</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>0.0371427866031282</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>0.0444650031634004</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.0197291410697962</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>0.146712283408501</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>0.307148131804351</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>179.63</t>
+          <t>1.79645044268856</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>152.99</t>
+          <t>1.53001007147552</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>144.04</t>
+          <t>1.44051565291172</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>140.63</t>
+          <t>1.40625541450116</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>122.87</t>
+          <t>1.19289091122869</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>159.84</t>
+          <t>1.59857781019813</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>179.12</t>
+          <t>1.79153581068793</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>217.99</t>
+          <t>2.18036779102972</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>205.61</t>
+          <t>2.05631134174357</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>187.87</t>
+          <t>1.87875237640444</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>2.0850739573285</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>223.07</t>
+          <t>2.23100206349164</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>218.52</t>
+          <t>2.18558181748482</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>0.879145503919465</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>108.8</t>
+          <t>1.08805449713006</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>0.656838272108179</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>0.547815354615055</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>0.742983174158081</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>0.81351833559017</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>0.81762167881638</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>75.81</t>
+          <t>0.758296520822136</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>0.697267393969322</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>0.738064776925474</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>74.04</t>
+          <t>0.740601358099912</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>77.77</t>
+          <t>0.77779817491347</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>0.801727293164991</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>86.83</t>
+          <t>0.868301176754291</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>109.2</t>
+          <t>1.09225103131285</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>1.10505492866987</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>132.31</t>
+          <t>1.32304990752198</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>0.750041678669464</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>0.784965503653411</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>78.11</t>
+          <t>0.781539265055525</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>0.691918834295256</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>64.41</t>
+          <t>0.627050305166527</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>48.91</t>
+          <t>0.489288763242194</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>0.429263258076276</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>0.388358711763847</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>33.94</t>
+          <t>0.339532619177777</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>0.31377219476833</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>30.97</t>
+          <t>0.309572815630473</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>0.344894232465397</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>44.75</t>
+          <t>0.447842119568148</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>53.99</t>
+          <t>0.539739383625722</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>56.79</t>
+          <t>0.567941267781189</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.00480490595178273</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>0.0478847716702522</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>0.0398752527409634</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>0.0355005509549113</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>0.00696940985246175</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.00489625398066873</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.0194388640966219</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.0194491950191997</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>0.051141640923956</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>0.115931061628529</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>0.0974565918057853</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>0.0971070898038187</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>17.82</t>
+          <t>0.178253189050831</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>21.02</t>
+          <t>0.210150021920398</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>0.234755918917144</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>0.165099996020552</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>0.219405762270875</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>0.242510485919611</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>0.248236050369538</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>0.240887098067762</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>0.257588485210884</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>0.275246526480933</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>0.289991120482616</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>0.292386259300887</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>0.321078810810772</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>0.316486888714276</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>32.52</t>
+          <t>0.325241329756106</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>0.401536317299444</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>0.431128220689277</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>0.452391818284521</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
